--- a/resampling/input/accessibility_reports_returned/CRS_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/CRS_accessibility_report.xlsx
@@ -210,8 +210,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O177" headerRowCount="1">
-  <autoFilter ref="A1:O177"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O252" headerRowCount="1">
+  <autoFilter ref="A1:O252"/>
   <tableColumns count="15">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -10586,7 +10586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O177"/>
+  <dimension ref="A1:O252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17571,23 +17571,2964 @@
       </c>
       <c r="M177" s="10" t="inlineStr"/>
     </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Agatu</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Loko</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>non_idp_NG007002_supp2</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Agatu</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Mbapupuu / Tswarev</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>non_idp_NG007002_supp3</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Gwer West</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Odugbeho</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>non_idp_NG007008_supp1</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Gwer West</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Mbachohon</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>non_idp_NG007008_supp2</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Gwer West</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Ugee</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>non_idp_NG007008_supp4</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Gwer West</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Mbasombo</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>non_idp_NG007008_supp5</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Gwer West</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Nyamshi / Mbanyamshi</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>non_idp_NG007008_supp6</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Gwer West</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Mbasombo</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>non_idp_NG007008_supp7</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Gwer West</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Mbasombo</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>non_idp_NG007008_supp8</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Logo</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Mbavuur</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>non_idp_NG007012_supp1</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Logo</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Mbayam</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>non_idp_NG007012_supp4</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Bokkos</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Mangun</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>non_idp_NG032003_supp4</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Logo</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Mbavuur</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>non_idp_NG007012_supp3</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Logo</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Mbadyul</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>non_idp_NG007012_supp5</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Logo</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Iwar</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>non_idp_NG007012_supp6</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Logo</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Mbadyul</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>non_idp_NG007012_supp7</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Barikin Ladi</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Lobring</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>non_idp_NG032001_supp1</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Barikin Ladi</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Heipang</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>non_idp_NG032001_supp2</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Barikin Ladi</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Heipang</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>non_idp_NG032001_supp3</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Barikin Ladi</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Zabot</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>non_idp_NG032001_supp4</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Barikin Ladi</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Zabot</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>non_idp_NG032001_supp5</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Barikin Ladi</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Lobring</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>non_idp_NG032001_supp6</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Barikin Ladi</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Lobring</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>non_idp_NG032001_supp7</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Bassa</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Zabolo</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>non_idp_NG032002_supp1</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Bassa</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Jengere</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>non_idp_NG032002_supp2</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Bassa</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Jengere</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>non_idp_NG032002_supp3</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Bassa</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Zabolo</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>non_idp_NG032002_supp4</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Bokkos</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Daffo</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>non_idp_NG032003_supp2</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Bokkos</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Daffo</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>non_idp_NG032003_supp3</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Bokkos</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Daffo</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>non_idp_NG032003_supp5</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Bokkos</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Daffo</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>non_idp_NG032003_supp6</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Bokkos</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Bokkos Central</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>non_idp_NG032003_supp7</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Koko/Besse</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Damba Bakoshi</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>non_idp_NG022013_supp1</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Koko/Besse</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Matsinkai Geza</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>non_idp_NG022013_supp2</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Koko/Besse</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Koko Firchin</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>non_idp_NG022013_supp3</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Koko/Besse</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Matsinkai Geza</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>non_idp_NG022013_supp5</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Koko/Besse</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Damba Bakoshi</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>non_idp_NG022013_supp6</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Koko/Besse</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Damba Bakoshi</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>non_idp_NG022013_supp7</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Shagari</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Shagari</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>non_idp_NG034014_supp1</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Shagari</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Bengaje</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>non_idp_NG034014_supp2</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Shagari</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Bangi Dabaga</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>non_idp_NG034014_supp3</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Shagari</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Birnin Magaji</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>non_idp_NG034014_supp5</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Wamako</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Arkilla</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>non_idp_NG034021_supp2</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Wamako</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Dundaye</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>non_idp_NG034021_supp4</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Wamako</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Gagi B</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>non_idp_NG034021_supp5</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Agatu</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Oshigbudu</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>non_idp_NG007002_supp4</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Shagari</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Shagari</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>non_idp_NG034014_supp6</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Agatu</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Oshigbudu</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>non_idp_NG007002_supp5</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Agatu</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Loko</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>non_idp_NG007002_supp6</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Agatu</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Ojantelle / Akpete</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>non_idp_NG007002_supp7</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Agatu</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Loko</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>non_idp_NG007002_supp8</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Shagari</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Shagari</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>non_idp_NG034014_supp7</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Agatu</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Oshigbudu</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>idp_NG007002_supp1</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Agatu</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Oshigbudu</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>idp_NG007002_supp2</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Gwer West</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Ikyaghev</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>idp_NG007008_supp1</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Gwer West</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Ikyaghev</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>idp_NG007008_supp2</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Gwer West</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Ikyaghev</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>idp_NG007008_supp3</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Gwer West</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Ikyaghev</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>idp_NG007008_supp4</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Gwer West</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Ikyaghev</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>idp_NG007008_supp5</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Gwer West</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Ikyaghev</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>idp_NG007008_supp6</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Gwer West</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Ikyaghev</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>idp_NG007008_supp7</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Gwer West</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Mbachohon</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>idp_NG007008_supp8</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Gwer West</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Mbachohon</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>idp_NG007008_supp9</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Logo</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Mbagber</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>idp_NG007012_supp1</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Logo</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Mbagber</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>idp_NG007012_supp2</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Logo</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Mbagber</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>idp_NG007012_supp3</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Logo</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Mbagber</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>idp_NG007012_supp4</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Logo</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Mbayam</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>idp_NG007012_supp5</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Bassa</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Tahu</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>idp_NG032002_supp1</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Shagari</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Shagari</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>idp_NG034014_supp1</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Shagari</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Shagari</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>idp_NG034014_supp2</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Shagari</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Shagari</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>idp_NG034014_supp3</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Wamako</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Arkilla</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>idp_NG034021_supp1</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Wamako</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Arkilla</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>idp_NG034021_supp2</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Wamako</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Arkilla</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>idp_NG034021_supp3</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="I2:I177" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I252" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J177" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J252" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N177" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N252" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O177" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O252" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M177" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+    <dataValidation sqref="M2:M252" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-08-28</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17853,13 +20794,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68E806FF-8274-4A2C-B1FC-3792F3AFCB89}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3702FA69-E89A-44EC-AF1C-E96249583310}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7630A7A-5A25-44F3-818F-2326E4163388}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D36EA72-5355-4858-9FE9-2C65402F289E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40BC5E0E-61C5-4142-A0C0-B183583BF872}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40A5B97C-740F-43D2-93B6-A12B8D82870C}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/CRS_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/CRS_accessibility_report.xlsx
@@ -210,8 +210,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O252" headerRowCount="1">
-  <autoFilter ref="A1:O252"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O269" headerRowCount="1">
+  <autoFilter ref="A1:O269"/>
   <tableColumns count="15">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -10586,7 +10586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O252"/>
+  <dimension ref="A1:O269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17597,7 +17597,6 @@
           <t>non_idp_NG007002_supp2</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr">
         <is>
           <t>6</t>
@@ -17635,7 +17634,6 @@
           <t>non_idp_NG007002_supp3</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr">
         <is>
           <t>6</t>
@@ -17673,7 +17671,6 @@
           <t>non_idp_NG007008_supp1</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr">
         <is>
           <t>6</t>
@@ -17711,7 +17708,6 @@
           <t>non_idp_NG007008_supp2</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
           <t>6</t>
@@ -17749,7 +17745,6 @@
           <t>non_idp_NG007008_supp4</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr">
         <is>
           <t>6</t>
@@ -17787,7 +17782,6 @@
           <t>non_idp_NG007008_supp5</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr">
         <is>
           <t>6</t>
@@ -17825,7 +17819,6 @@
           <t>non_idp_NG007008_supp6</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
           <t>6</t>
@@ -17863,7 +17856,6 @@
           <t>non_idp_NG007008_supp7</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr">
         <is>
           <t>6</t>
@@ -17901,7 +17893,6 @@
           <t>non_idp_NG007008_supp8</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr">
         <is>
           <t>6</t>
@@ -17939,7 +17930,6 @@
           <t>non_idp_NG007012_supp1</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
           <t>6</t>
@@ -17977,7 +17967,6 @@
           <t>non_idp_NG007012_supp4</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
           <t>6</t>
@@ -18015,7 +18004,6 @@
           <t>non_idp_NG032003_supp4</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
           <t>6</t>
@@ -18053,7 +18041,6 @@
           <t>non_idp_NG007012_supp3</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
         <is>
           <t>6</t>
@@ -18091,7 +18078,6 @@
           <t>non_idp_NG007012_supp5</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
           <t>6</t>
@@ -18129,7 +18115,6 @@
           <t>non_idp_NG007012_supp6</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
           <t>6</t>
@@ -18167,7 +18152,6 @@
           <t>non_idp_NG007012_supp7</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
           <t>6</t>
@@ -18205,7 +18189,6 @@
           <t>non_idp_NG032001_supp1</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
           <t>6</t>
@@ -18243,7 +18226,6 @@
           <t>non_idp_NG032001_supp2</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
           <t>6</t>
@@ -18281,7 +18263,6 @@
           <t>non_idp_NG032001_supp3</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
           <t>6</t>
@@ -18319,7 +18300,6 @@
           <t>non_idp_NG032001_supp4</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
           <t>6</t>
@@ -18357,7 +18337,6 @@
           <t>non_idp_NG032001_supp5</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
           <t>6</t>
@@ -18395,7 +18374,6 @@
           <t>non_idp_NG032001_supp6</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
           <t>6</t>
@@ -18433,7 +18411,6 @@
           <t>non_idp_NG032001_supp7</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr">
         <is>
           <t>6</t>
@@ -18471,7 +18448,6 @@
           <t>non_idp_NG032002_supp1</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr">
         <is>
           <t>6</t>
@@ -18509,7 +18485,6 @@
           <t>non_idp_NG032002_supp2</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr">
         <is>
           <t>6</t>
@@ -18547,7 +18522,6 @@
           <t>non_idp_NG032002_supp3</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr">
         <is>
           <t>6</t>
@@ -18585,7 +18559,6 @@
           <t>non_idp_NG032002_supp4</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr">
         <is>
           <t>6</t>
@@ -18623,7 +18596,6 @@
           <t>non_idp_NG032003_supp2</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr">
         <is>
           <t>6</t>
@@ -18661,7 +18633,6 @@
           <t>non_idp_NG032003_supp3</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr">
         <is>
           <t>6</t>
@@ -18699,7 +18670,6 @@
           <t>non_idp_NG032003_supp5</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr">
         <is>
           <t>6</t>
@@ -18737,7 +18707,6 @@
           <t>non_idp_NG032003_supp6</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr">
         <is>
           <t>6</t>
@@ -18775,7 +18744,6 @@
           <t>non_idp_NG032003_supp7</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr">
         <is>
           <t>6</t>
@@ -18813,7 +18781,6 @@
           <t>non_idp_NG022013_supp1</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr">
         <is>
           <t>6</t>
@@ -18851,7 +18818,6 @@
           <t>non_idp_NG022013_supp2</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr">
         <is>
           <t>6</t>
@@ -18889,7 +18855,6 @@
           <t>non_idp_NG022013_supp3</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr"/>
       <c r="G212" t="inlineStr">
         <is>
           <t>6</t>
@@ -18927,7 +18892,6 @@
           <t>non_idp_NG022013_supp5</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr">
         <is>
           <t>6</t>
@@ -18965,7 +18929,6 @@
           <t>non_idp_NG022013_supp6</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr">
         <is>
           <t>6</t>
@@ -19003,7 +18966,6 @@
           <t>non_idp_NG022013_supp7</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr"/>
       <c r="G215" t="inlineStr">
         <is>
           <t>6</t>
@@ -19041,7 +19003,6 @@
           <t>non_idp_NG034014_supp1</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr">
         <is>
           <t>6</t>
@@ -19079,7 +19040,6 @@
           <t>non_idp_NG034014_supp2</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr">
         <is>
           <t>6</t>
@@ -19117,7 +19077,6 @@
           <t>non_idp_NG034014_supp3</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr">
         <is>
           <t>6</t>
@@ -19155,7 +19114,6 @@
           <t>non_idp_NG034014_supp5</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr">
         <is>
           <t>6</t>
@@ -19193,7 +19151,6 @@
           <t>non_idp_NG034021_supp2</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr">
         <is>
           <t>6</t>
@@ -19231,7 +19188,6 @@
           <t>non_idp_NG034021_supp4</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr"/>
       <c r="G221" t="inlineStr">
         <is>
           <t>6</t>
@@ -19269,7 +19225,6 @@
           <t>non_idp_NG034021_supp5</t>
         </is>
       </c>
-      <c r="F222" t="inlineStr"/>
       <c r="G222" t="inlineStr">
         <is>
           <t>6</t>
@@ -19307,7 +19262,6 @@
           <t>non_idp_NG007002_supp4</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr"/>
       <c r="G223" t="inlineStr">
         <is>
           <t>6</t>
@@ -19345,7 +19299,6 @@
           <t>non_idp_NG034014_supp6</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr">
         <is>
           <t>6</t>
@@ -19383,7 +19336,6 @@
           <t>non_idp_NG007002_supp5</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr"/>
       <c r="G225" t="inlineStr">
         <is>
           <t>12</t>
@@ -19421,7 +19373,6 @@
           <t>non_idp_NG007002_supp6</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr">
         <is>
           <t>12</t>
@@ -19459,7 +19410,6 @@
           <t>non_idp_NG007002_supp7</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr">
         <is>
           <t>12</t>
@@ -19497,7 +19447,6 @@
           <t>non_idp_NG007002_supp8</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr">
         <is>
           <t>12</t>
@@ -19535,7 +19484,6 @@
           <t>non_idp_NG034014_supp7</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr">
         <is>
           <t>12</t>
@@ -20513,21 +20461,667 @@
         </is>
       </c>
     </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Gwer West</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Ikyaghev</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>non_idp_NG007008_supp10</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Gwer West</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Mbalom</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>non_idp_NG007008_supp11</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Logo</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Mbavuur</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>non_idp_NG007012_supp8</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Koko/Besse</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Koko Firchin</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>non_idp_NG022013_supp11</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Koko/Besse</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Matsinkai Geza</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>non_idp_NG022013_supp12</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Koko/Besse</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Sharabi Kwanguwai</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>non_idp_NG022013_supp13</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Koko/Besse</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Sharabi Kwanguwai</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>non_idp_NG022013_supp14</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Koko/Besse</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Damba Bakoshi</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>non_idp_NG022013_supp15</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Koko/Besse</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Kende Kurgu</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>non_idp_NG022013_supp16</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Wamako</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Kubodu</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>non_idp_NG034021_supp6</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Wamako</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Bankanu</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>non_idp_NG034021_supp7</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Agatu</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Oshigbudu</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>non_idp_NG007002_supp9</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Agatu</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Loko</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>non_idp_NG007002_supp10</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Agatu</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Loko</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>non_idp_NG007002_supp11</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Shagari</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Shagari</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>non_idp_NG034014_supp9</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Shagari</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Shagari</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>non_idp_NG034014_supp10</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Shagari</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Shagari</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>non_idp_NG034014_supp11</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="I2:I252" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I269" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J252" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J269" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N252" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N269" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O252" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O269" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M252" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date">
+    <dataValidation sqref="M2:M269" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date">
       <formula1>2026-07-01</formula1>
     </dataValidation>
   </dataValidations>
@@ -20536,271 +21130,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
-    <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
-    <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="30973102-2308-455b-8e1f-b6a90edc3b23" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{daf5bdda-bc47-491d-9935-b3e42d5c0ae4}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="947c1918-d5ab-48a1-8b61-0d52f2f99fd1">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="30973102-2308-455b-8e1f-b6a90edc3b23">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3702FA69-E89A-44EC-AF1C-E96249583310}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D36EA72-5355-4858-9FE9-2C65402F289E}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40A5B97C-740F-43D2-93B6-A12B8D82870C}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/CRS_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/CRS_accessibility_report.xlsx
@@ -21130,4 +21130,271 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
+    <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
+    <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="30973102-2308-455b-8e1f-b6a90edc3b23" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{daf5bdda-bc47-491d-9935-b3e42d5c0ae4}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="947c1918-d5ab-48a1-8b61-0d52f2f99fd1">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="30973102-2308-455b-8e1f-b6a90edc3b23">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12B15A3E-958D-4F92-85C2-E4C387BCC56D}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D3FFCD0-930F-4A54-A911-737453E4E3DB}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24B1FB6B-5FE3-4196-A74A-01663D200F0B}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/CRS_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/CRS_accessibility_report.xlsx
@@ -18,8 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -89,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -107,6 +108,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4400,10 +4402,22 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O96" s="10" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Source: CRS report 2509 (CRS covering partner) accepted by Jack Philpott 2026-09-26</t>
+        </is>
+      </c>
+      <c r="O96" s="10" t="n">
+        <v>46290</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9652,6 +9666,24 @@
       <c r="J228" t="n">
         <v>0</v>
       </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>Source: CRS report 2509 (CRS covering partner) accepted by Jack Philpott 2026-09-26</t>
+        </is>
+      </c>
+      <c r="O228" s="11" t="n">
+        <v>46290</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -9693,6 +9725,24 @@
       <c r="J229" t="n">
         <v>0</v>
       </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>Source: CRS report 2509 (CRS covering partner) accepted by Jack Philpott 2026-09-26</t>
+        </is>
+      </c>
+      <c r="O229" s="11" t="n">
+        <v>46290</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -9734,6 +9784,24 @@
       <c r="J230" t="n">
         <v>0</v>
       </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>Source: CRS report 2509 (CRS covering partner) accepted by Jack Philpott 2026-09-26</t>
+        </is>
+      </c>
+      <c r="O230" s="11" t="n">
+        <v>46290</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -9775,6 +9843,24 @@
       <c r="J231" t="n">
         <v>0</v>
       </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>Source: CRS report 2509 (CRS covering partner) accepted by Jack Philpott 2026-09-26</t>
+        </is>
+      </c>
+      <c r="O231" s="11" t="n">
+        <v>46290</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -9816,6 +9902,24 @@
       <c r="J232" t="n">
         <v>0</v>
       </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>Source: CRS report 2509 (CRS covering partner) accepted by Jack Philpott 2026-09-26</t>
+        </is>
+      </c>
+      <c r="O232" s="11" t="n">
+        <v>46290</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -9857,6 +9961,24 @@
       <c r="J233" t="n">
         <v>0</v>
       </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>Source: CRS report 2509 (CRS covering partner) accepted by Jack Philpott 2026-09-26</t>
+        </is>
+      </c>
+      <c r="O233" s="11" t="n">
+        <v>46290</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -9898,6 +10020,24 @@
       <c r="J234" t="n">
         <v>0</v>
       </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>Source: CRS report 2509 (CRS covering partner) accepted by Jack Philpott 2026-09-26</t>
+        </is>
+      </c>
+      <c r="O234" s="11" t="n">
+        <v>46290</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -9938,6 +10078,24 @@
       </c>
       <c r="J235" t="n">
         <v>0</v>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>Source: CRS report 2509 (CRS covering partner) accepted by Jack Philpott 2026-09-26</t>
+        </is>
+      </c>
+      <c r="O235" s="11" t="n">
+        <v>46290</v>
       </c>
     </row>
     <row r="236">
@@ -20487,7 +20645,6 @@
           <t>non_idp_NG007008_supp10</t>
         </is>
       </c>
-      <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr">
         <is>
           <t>6</t>
@@ -20525,7 +20682,6 @@
           <t>non_idp_NG007008_supp11</t>
         </is>
       </c>
-      <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr">
         <is>
           <t>6</t>
@@ -20563,7 +20719,6 @@
           <t>non_idp_NG007012_supp8</t>
         </is>
       </c>
-      <c r="F255" t="inlineStr"/>
       <c r="G255" t="inlineStr">
         <is>
           <t>6</t>
@@ -20601,7 +20756,6 @@
           <t>non_idp_NG022013_supp11</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr">
         <is>
           <t>6</t>
@@ -20639,7 +20793,6 @@
           <t>non_idp_NG022013_supp12</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr">
         <is>
           <t>6</t>
@@ -20677,7 +20830,6 @@
           <t>non_idp_NG022013_supp13</t>
         </is>
       </c>
-      <c r="F258" t="inlineStr"/>
       <c r="G258" t="inlineStr">
         <is>
           <t>6</t>
@@ -20715,7 +20867,6 @@
           <t>non_idp_NG022013_supp14</t>
         </is>
       </c>
-      <c r="F259" t="inlineStr"/>
       <c r="G259" t="inlineStr">
         <is>
           <t>6</t>
@@ -20753,7 +20904,6 @@
           <t>non_idp_NG022013_supp15</t>
         </is>
       </c>
-      <c r="F260" t="inlineStr"/>
       <c r="G260" t="inlineStr">
         <is>
           <t>6</t>
@@ -20791,7 +20941,6 @@
           <t>non_idp_NG022013_supp16</t>
         </is>
       </c>
-      <c r="F261" t="inlineStr"/>
       <c r="G261" t="inlineStr">
         <is>
           <t>6</t>
@@ -20829,7 +20978,6 @@
           <t>non_idp_NG034021_supp6</t>
         </is>
       </c>
-      <c r="F262" t="inlineStr"/>
       <c r="G262" t="inlineStr">
         <is>
           <t>6</t>
@@ -20867,7 +21015,6 @@
           <t>non_idp_NG034021_supp7</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr"/>
       <c r="G263" t="inlineStr">
         <is>
           <t>6</t>
@@ -20905,7 +21052,6 @@
           <t>non_idp_NG007002_supp9</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr"/>
       <c r="G264" t="inlineStr">
         <is>
           <t>6</t>
@@ -20943,7 +21089,6 @@
           <t>non_idp_NG007002_supp10</t>
         </is>
       </c>
-      <c r="F265" t="inlineStr"/>
       <c r="G265" t="inlineStr">
         <is>
           <t>6</t>
@@ -20981,7 +21126,6 @@
           <t>non_idp_NG007002_supp11</t>
         </is>
       </c>
-      <c r="F266" t="inlineStr"/>
       <c r="G266" t="inlineStr">
         <is>
           <t>6</t>
@@ -21019,7 +21163,6 @@
           <t>non_idp_NG034014_supp9</t>
         </is>
       </c>
-      <c r="F267" t="inlineStr"/>
       <c r="G267" t="inlineStr">
         <is>
           <t>6</t>
@@ -21057,7 +21200,6 @@
           <t>non_idp_NG034014_supp10</t>
         </is>
       </c>
-      <c r="F268" t="inlineStr"/>
       <c r="G268" t="inlineStr">
         <is>
           <t>6</t>
@@ -21095,7 +21237,6 @@
           <t>non_idp_NG034014_supp11</t>
         </is>
       </c>
-      <c r="F269" t="inlineStr"/>
       <c r="G269" t="inlineStr">
         <is>
           <t>6</t>
@@ -21388,13 +21529,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12B15A3E-958D-4F92-85C2-E4C387BCC56D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69EDEAF1-05A5-4B91-B4F9-BE3CB9115311}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D3FFCD0-930F-4A54-A911-737453E4E3DB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE0FA27D-E459-4E41-B5F3-6CC526BDE2DC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24B1FB6B-5FE3-4196-A74A-01663D200F0B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3A3B5FC-5C8D-4C01-B33A-1FA2ED6187E0}"/>
 </file>